--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/0052-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/0052-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CBC7C1D-F389-4667-A4B5-569B6788B9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AC10825-7AE5-489F-947D-B88E121F358B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8D70CEBE-C28C-4933-90E8-B9A6D6EAC7C8}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{48B84440-636C-47EA-B213-4FDB92000238}"/>
   </bookViews>
   <sheets>
     <sheet name="0052-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1451,29 +1451,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2105B10A-5DE3-4489-B88B-B4A1BA9AD696}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1F66AD-01BB-4A2C-84DC-D753894D3B2E}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.625" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="5.875" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="5.875" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="5.875" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="5.875" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="5.875" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="5.875" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1507,7 +1506,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1543,7 +1542,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1595,7 +1594,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1663,7 +1662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1735,7 +1734,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1879,7 +1878,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1951,7 +1950,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2023,7 +2022,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2095,7 +2094,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2167,7 +2166,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2239,7 +2238,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2527,7 +2526,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2743,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2887,7 +2886,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2959,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3031,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>43</v>
       </c>
